--- a/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -400,6 +400,16 @@
           <t>6</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -435,6 +445,12 @@
       <c r="I2">
         <v>25</v>
       </c>
+      <c r="J2">
+        <v>82</v>
+      </c>
+      <c r="K2">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -461,6 +477,12 @@
       <c r="I3">
         <v>86</v>
       </c>
+      <c r="J3">
+        <v>176</v>
+      </c>
+      <c r="K3">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -481,6 +503,12 @@
       <c r="I4">
         <v>0</v>
       </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -516,6 +544,12 @@
       <c r="I5">
         <v>1</v>
       </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -551,6 +585,12 @@
       <c r="I6">
         <v>84</v>
       </c>
+      <c r="J6">
+        <v>96</v>
+      </c>
+      <c r="K6">
+        <v>86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -586,6 +626,12 @@
       <c r="I7">
         <v>27</v>
       </c>
+      <c r="J7">
+        <v>51</v>
+      </c>
+      <c r="K7">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -621,6 +667,12 @@
       <c r="I8">
         <v>22</v>
       </c>
+      <c r="J8">
+        <v>30</v>
+      </c>
+      <c r="K8">
+        <v>32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -656,6 +708,12 @@
       <c r="I9">
         <v>2</v>
       </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -691,6 +749,12 @@
       <c r="I10">
         <v>3</v>
       </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -714,6 +778,12 @@
       <c r="I11">
         <v>1</v>
       </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -734,6 +804,12 @@
       <c r="G12">
         <v>2</v>
       </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -763,6 +839,12 @@
       <c r="I13">
         <v>1</v>
       </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -795,6 +877,12 @@
       <c r="H14">
         <v>9</v>
       </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -821,6 +909,12 @@
       <c r="I15">
         <v>1</v>
       </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -830,22 +924,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CAIMALITO</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>4</v>
-      </c>
-      <c r="H16">
-        <v>4</v>
-      </c>
-      <c r="I16">
-        <v>3</v>
+          <t>PUESTO DE SALUD PUERTO CALDAS</t>
+        </is>
+      </c>
+      <c r="J16">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -856,19 +944,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD LA BELLA</t>
-        </is>
-      </c>
-      <c r="F17">
-        <v>1</v>
+          <t>PUESTO DE SALUD CAIMALITO</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -879,22 +976,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ARABIA</t>
+          <t>PUESTO DE SALUD LA BELLA</t>
         </is>
       </c>
       <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -905,28 +1002,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ALTAGRACIA</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
+          <t>PUESTO DE SALUD ARABIA</t>
+        </is>
       </c>
       <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
         <v>3</v>
       </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
       <c r="H19">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -937,31 +1031,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HOSPITAL DEL CENTRO</t>
+          <t>PUESTO DE SALUD ALTAGRACIA</t>
         </is>
       </c>
       <c r="D20">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>34</v>
-      </c>
-      <c r="I20">
-        <v>43</v>
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>7</v>
+      </c>
+      <c r="K20">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -972,98 +1069,95 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD CASA DEL ABUELO</t>
+          <t>HOSPITAL DEL CENTRO</t>
         </is>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="E21">
+        <v>21</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>37</v>
+      </c>
+      <c r="H21">
+        <v>34</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="J21">
+        <v>47</v>
+      </c>
+      <c r="K21">
+        <v>45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6600100361</t>
+          <t>6600100332</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLINICA LOS ROSALES</t>
+          <t>CENTRO DE SALUD CASA DEL ABUELO</t>
         </is>
       </c>
       <c r="D22">
-        <v>184</v>
-      </c>
-      <c r="E22">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>146</v>
-      </c>
-      <c r="H22">
-        <v>171</v>
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6600100663</t>
+          <t>6600100332</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ONCOLOGOS DEL OCCIDENTE SA</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
+          <t>CENTRO DE SALUD EL REMANSO</t>
+        </is>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6600100762</t>
+          <t>6600100361</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1073,102 +1167,99 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ESE HOSPITAL UNIVERSITARIO SAN JORGE DE PEREIRA</t>
+          <t>CLINICA LOS ROSALES</t>
         </is>
       </c>
       <c r="D24">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="E24">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="F24">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="G24">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="H24">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="I24">
-        <v>54</v>
+        <v>174</v>
+      </c>
+      <c r="J24">
+        <v>386</v>
+      </c>
+      <c r="K24">
+        <v>214</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6600100785</t>
+          <t>6600100532</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FUNDACIÓN LA LIGA AMA SALVAR VIDAS</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-      <c r="G25">
-        <v>7</v>
-      </c>
-      <c r="H25">
-        <v>4</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
+          <t>QUIRÓFANO CASALUD SAS</t>
+        </is>
+      </c>
+      <c r="K25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6600101587</t>
+          <t>6600100663</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS Y SERVICIOS M</t>
+          <t>ONCOLOGOS DEL OCCIDENTE SA</t>
         </is>
       </c>
       <c r="D26">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6600101736</t>
+          <t>6600100762</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1178,32 +1269,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MEDICA SALUD PARA LOS COLOMBIANOS - CM</t>
+          <t>ESE HOSPITAL UNIVERSITARIO SAN JORGE DE PEREIRA</t>
         </is>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="G27">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="I27">
-        <v>13</v>
+        <v>54</v>
+      </c>
+      <c r="J27">
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6600101781</t>
+          <t>6600100785</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,113 +1307,161 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SINERGIA GLOBAL EN SALUD SAS</t>
+          <t>FUNDACIÓN LA LIGA AMA SALVAR VIDAS</t>
         </is>
       </c>
       <c r="D28">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>7</v>
       </c>
       <c r="H28">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I28">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6600101912</t>
+          <t>6600101587</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RED MEDICA VITAL SAS</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS Y SERVICIOS M</t>
         </is>
       </c>
       <c r="D29">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E29">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F29">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G29">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H29">
+        <v>40</v>
+      </c>
+      <c r="I29">
         <v>34</v>
       </c>
-      <c r="I29">
-        <v>59</v>
+      <c r="J29">
+        <v>68</v>
+      </c>
+      <c r="K29">
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6600102402</t>
+          <t>6600101736</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
-        </is>
+          <t>CORPORACIÓN MEDICA SALUD PARA LOS COLOMBIANOS - CM</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>13</v>
+      </c>
+      <c r="J30">
+        <v>25</v>
+      </c>
+      <c r="K30">
+        <v>42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6600102411</t>
+          <t>6600101781</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
-        </is>
+          <t>SINERGIA GLOBAL EN SALUD SAS</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>19</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>7</v>
       </c>
       <c r="H31">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <v>13</v>
+      </c>
+      <c r="K31">
         <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6600102446</t>
+          <t>6600101912</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1329,67 +1471,58 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
+          <t>RED MEDICA VITAL SAS</t>
         </is>
       </c>
       <c r="D32">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E32">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F32">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="G32">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="H32">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="I32">
+        <v>59</v>
+      </c>
+      <c r="J32">
         <v>71</v>
+      </c>
+      <c r="K32">
+        <v>110</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6600102446</t>
+          <t>6600102402</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>65</v>
-      </c>
-      <c r="E33">
-        <v>57</v>
-      </c>
-      <c r="F33">
-        <v>48</v>
+          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
+        </is>
       </c>
       <c r="G33">
-        <v>42</v>
-      </c>
-      <c r="H33">
-        <v>48</v>
-      </c>
-      <c r="I33">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6600102453</t>
+          <t>6600102411</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1399,32 +1532,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VITALCARE IPS SAS</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>13</v>
-      </c>
-      <c r="E34">
-        <v>8</v>
+          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
+        </is>
       </c>
       <c r="F34">
-        <v>15</v>
-      </c>
-      <c r="G34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="J34">
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6600102477</t>
+          <t>6600102446</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1434,131 +1561,155 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
+          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
         </is>
       </c>
       <c r="D35">
-        <v>308</v>
+        <v>108</v>
       </c>
       <c r="E35">
-        <v>263</v>
+        <v>61</v>
       </c>
       <c r="F35">
-        <v>238</v>
+        <v>123</v>
       </c>
       <c r="G35">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="H35">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="I35">
-        <v>207</v>
+        <v>71</v>
+      </c>
+      <c r="J35">
+        <v>97</v>
+      </c>
+      <c r="K35">
+        <v>98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6600102601</t>
+          <t>6600102446</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS SA PINARES</t>
+          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
         </is>
       </c>
       <c r="D36">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="E36">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="F36">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="G36">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="H36">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="I36">
-        <v>90</v>
+        <v>39</v>
+      </c>
+      <c r="J36">
+        <v>44</v>
+      </c>
+      <c r="K36">
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6600102601</t>
+          <t>6600102453</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS LAGO</t>
+          <t>VITALCARE IPS SAS</t>
         </is>
       </c>
       <c r="D37">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>188</v>
+        <v>15</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H37">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>134</v>
+        <v>19</v>
+      </c>
+      <c r="J37">
+        <v>14</v>
+      </c>
+      <c r="K37">
+        <v>29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6600102601</t>
+          <t>6600102477</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA ALPES</t>
+          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
         </is>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>210</v>
       </c>
       <c r="E38">
-        <v>9</v>
+        <v>190</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>172</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>173</v>
+      </c>
+      <c r="J38">
+        <v>166</v>
+      </c>
+      <c r="K38">
+        <v>182</v>
       </c>
     </row>
     <row r="39">
@@ -1569,31 +1720,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA LA REBECA</t>
+          <t>VIRREY SOLIS SA PINARES</t>
         </is>
       </c>
       <c r="D39">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E39">
+        <v>83</v>
+      </c>
+      <c r="F39">
+        <v>128</v>
+      </c>
+      <c r="G39">
+        <v>54</v>
+      </c>
+      <c r="H39">
         <v>93</v>
       </c>
-      <c r="F39">
-        <v>95</v>
-      </c>
-      <c r="G39">
-        <v>44</v>
-      </c>
-      <c r="H39">
-        <v>119</v>
-      </c>
       <c r="I39">
-        <v>77</v>
+        <v>90</v>
+      </c>
+      <c r="J39">
+        <v>98</v>
+      </c>
+      <c r="K39">
+        <v>59</v>
       </c>
     </row>
     <row r="40">
@@ -1604,124 +1761,151 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA CERRITOS</t>
-        </is>
+          <t>VIRREY SOLIS IPS LAGO</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>154</v>
+      </c>
+      <c r="E40">
+        <v>151</v>
+      </c>
+      <c r="F40">
+        <v>188</v>
+      </c>
+      <c r="G40">
+        <v>100</v>
+      </c>
+      <c r="H40">
+        <v>127</v>
       </c>
       <c r="I40">
-        <v>15</v>
+        <v>134</v>
+      </c>
+      <c r="J40">
+        <v>147</v>
+      </c>
+      <c r="K40">
+        <v>165</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6600102793</t>
+          <t>6600102601</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
+          <t>VIRREY SOLIS IPS SA ALPES</t>
         </is>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F41">
         <v>3</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41">
         <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6600102893</t>
+          <t>6600102601</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NEUROMEDICA SAS</t>
+          <t>VIRREY SOLIS IPS SA LA REBECA</t>
         </is>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="J42">
+        <v>87</v>
+      </c>
+      <c r="K42">
+        <v>115</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6600103012</t>
+          <t>6600102601</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>8</v>
-      </c>
-      <c r="E43">
-        <v>24</v>
-      </c>
-      <c r="G43">
-        <v>6</v>
-      </c>
-      <c r="H43">
-        <v>7</v>
+          <t>VIRREY SOLIS IPS SA CERRITOS</t>
+        </is>
       </c>
       <c r="I43">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="J43">
+        <v>31</v>
+      </c>
+      <c r="K43">
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6600103078</t>
+          <t>6600102793</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1731,32 +1915,38 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
+          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
         </is>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>3</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>6</v>
       </c>
       <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="K44">
         <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6600103144</t>
+          <t>6600102893</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1766,17 +1956,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLINICA LOS NEVADOS SAS</t>
+          <t>NEUROMEDICA SAS</t>
         </is>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -1785,13 +1975,19 @@
         <v>0</v>
       </c>
       <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6600103334</t>
+          <t>6600103012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1801,32 +1997,35 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLINICA CENTRAL DEL EJE SAS</t>
+          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
         </is>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="J46">
+        <v>8</v>
+      </c>
+      <c r="K46">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6600103414</t>
+          <t>6600103078</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1836,67 +2035,79 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CLINICA MEDICA TURIN SAS</t>
+          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
         </is>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>3</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6600161600</t>
+          <t>6600103144</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EPMSC PEREIRA</t>
+          <t>CLINICA LOS NEVADOS SAS</t>
         </is>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6600171151</t>
+          <t>6600103334</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1906,61 +2117,193 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+          <t>CLINICA CENTRAL DEL EJE SAS</t>
         </is>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>316</v>
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>6600103414</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLINICA MEDICA TURIN SAS</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6600161600</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EPMSC PEREIRA</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>8</v>
+      </c>
+      <c r="F51">
+        <v>7</v>
+      </c>
+      <c r="G51">
+        <v>16</v>
+      </c>
+      <c r="H51">
+        <v>10</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
+      </c>
+      <c r="J51">
+        <v>9</v>
+      </c>
+      <c r="K51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6600171151</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52">
+        <v>29</v>
+      </c>
+      <c r="F52">
+        <v>11</v>
+      </c>
+      <c r="G52">
+        <v>16</v>
+      </c>
+      <c r="H52">
+        <v>88</v>
+      </c>
+      <c r="I52">
+        <v>316</v>
+      </c>
+      <c r="J52">
+        <v>9</v>
+      </c>
+      <c r="K52">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>6600183029</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>BATALLON SAN MATEO</t>
         </is>
       </c>
-      <c r="D50">
+      <c r="D53">
         <v>7</v>
       </c>
-      <c r="E50">
+      <c r="E53">
         <v>11</v>
       </c>
-      <c r="F50">
+      <c r="F53">
         <v>13</v>
       </c>
-      <c r="G50">
+      <c r="G53">
         <v>19</v>
       </c>
-      <c r="H50">
+      <c r="H53">
         <v>25</v>
       </c>
-      <c r="I50">
+      <c r="I53">
         <v>26</v>
+      </c>
+      <c r="J53">
+        <v>43</v>
+      </c>
+      <c r="K53">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -410,6 +410,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -451,6 +456,9 @@
       <c r="K2">
         <v>32</v>
       </c>
+      <c r="L2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -483,6 +491,9 @@
       <c r="K3">
         <v>82</v>
       </c>
+      <c r="L3">
+        <v>168</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -550,6 +561,9 @@
       <c r="K5">
         <v>2</v>
       </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,6 +605,9 @@
       <c r="K6">
         <v>86</v>
       </c>
+      <c r="L6">
+        <v>966</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -632,6 +649,9 @@
       <c r="K7">
         <v>34</v>
       </c>
+      <c r="L7">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -673,6 +693,9 @@
       <c r="K8">
         <v>32</v>
       </c>
+      <c r="L8">
+        <v>39</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -714,6 +737,9 @@
       <c r="K9">
         <v>1</v>
       </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -784,6 +810,9 @@
       <c r="K11">
         <v>1</v>
       </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -810,6 +839,9 @@
       <c r="K12">
         <v>3</v>
       </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -845,6 +877,9 @@
       <c r="K13">
         <v>6</v>
       </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -883,6 +918,9 @@
       <c r="K14">
         <v>1</v>
       </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -915,6 +953,9 @@
       <c r="K15">
         <v>2</v>
       </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -967,6 +1008,9 @@
       <c r="K17">
         <v>2</v>
       </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1060,6 +1104,9 @@
       <c r="K20">
         <v>6</v>
       </c>
+      <c r="L20">
+        <v>6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1101,6 +1148,9 @@
       <c r="K21">
         <v>45</v>
       </c>
+      <c r="L21">
+        <v>60</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1153,6 +1203,9 @@
       <c r="K23">
         <v>2</v>
       </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1194,6 +1247,9 @@
       <c r="K24">
         <v>214</v>
       </c>
+      <c r="L24">
+        <v>442</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1214,6 +1270,9 @@
       <c r="K25">
         <v>0</v>
       </c>
+      <c r="L25">
+        <v>594</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,6 +1314,9 @@
       <c r="K26">
         <v>0</v>
       </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1293,6 +1355,12 @@
       <c r="J27">
         <v>94</v>
       </c>
+      <c r="K27">
+        <v>66</v>
+      </c>
+      <c r="L27">
+        <v>51</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1334,6 +1402,9 @@
       <c r="K28">
         <v>3</v>
       </c>
+      <c r="L28">
+        <v>12</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1375,6 +1446,9 @@
       <c r="K29">
         <v>43</v>
       </c>
+      <c r="L29">
+        <v>71</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1416,6 +1490,9 @@
       <c r="K30">
         <v>42</v>
       </c>
+      <c r="L30">
+        <v>56</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1457,6 +1534,9 @@
       <c r="K31">
         <v>11</v>
       </c>
+      <c r="L31">
+        <v>13</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1498,95 +1578,83 @@
       <c r="K32">
         <v>110</v>
       </c>
+      <c r="L32">
+        <v>51</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6600102402</t>
+          <t>6600102288</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
-        </is>
-      </c>
-      <c r="G33">
-        <v>2</v>
+          <t>SALUD PYP SAS</t>
+        </is>
+      </c>
+      <c r="K33">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6600102411</t>
+          <t>6600102402</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
-        </is>
-      </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
-      <c r="H34">
-        <v>9</v>
-      </c>
-      <c r="I34">
-        <v>11</v>
-      </c>
-      <c r="J34">
-        <v>18</v>
+          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6600102446</t>
+          <t>6600102411</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>108</v>
-      </c>
-      <c r="E35">
-        <v>61</v>
+          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
+        </is>
       </c>
       <c r="F35">
-        <v>123</v>
-      </c>
-      <c r="G35">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="H35">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="I35">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="J35">
-        <v>97</v>
-      </c>
-      <c r="K35">
-        <v>98</v>
+        <v>18</v>
+      </c>
+      <c r="L35">
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -1597,7 +1665,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1606,34 +1674,37 @@
         </is>
       </c>
       <c r="D36">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="E36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F36">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="G36">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="H36">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="I36">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="J36">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="K36">
-        <v>57</v>
+        <v>98</v>
+      </c>
+      <c r="L36">
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6600102453</t>
+          <t>6600102446</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1643,79 +1714,85 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VITALCARE IPS SAS</t>
+          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
         </is>
       </c>
       <c r="D37">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H37">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="I37">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J37">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="K37">
-        <v>29</v>
+        <v>57</v>
+      </c>
+      <c r="L37">
+        <v>112</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6600102477</t>
+          <t>6600102453</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
+          <t>VITALCARE IPS SAS</t>
         </is>
       </c>
       <c r="D38">
-        <v>210</v>
+        <v>13</v>
       </c>
       <c r="E38">
-        <v>190</v>
+        <v>8</v>
       </c>
       <c r="F38">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="G38">
-        <v>168</v>
+        <v>10</v>
       </c>
       <c r="H38">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="I38">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="J38">
-        <v>166</v>
+        <v>14</v>
       </c>
       <c r="K38">
-        <v>182</v>
+        <v>29</v>
+      </c>
+      <c r="L38">
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6600102601</t>
+          <t>6600102477</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1725,32 +1802,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS SA PINARES</t>
+          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
         </is>
       </c>
       <c r="D39">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="E39">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="F39">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="G39">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="H39">
-        <v>93</v>
+        <v>172</v>
       </c>
       <c r="I39">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="J39">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="K39">
-        <v>59</v>
+        <v>182</v>
+      </c>
+      <c r="L39">
+        <v>194</v>
       </c>
     </row>
     <row r="40">
@@ -1761,37 +1841,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS LAGO</t>
+          <t>VIRREY SOLIS SA PINARES</t>
         </is>
       </c>
       <c r="D40">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="E40">
-        <v>151</v>
+        <v>83</v>
       </c>
       <c r="F40">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="H40">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="I40">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="J40">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="K40">
-        <v>165</v>
+        <v>59</v>
+      </c>
+      <c r="L40">
+        <v>63</v>
       </c>
     </row>
     <row r="41">
@@ -1802,37 +1885,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA ALPES</t>
+          <t>VIRREY SOLIS IPS LAGO</t>
         </is>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="E41">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="J41">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>165</v>
+      </c>
+      <c r="L41">
+        <v>151</v>
       </c>
     </row>
     <row r="42">
@@ -1843,37 +1929,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA LA REBECA</t>
+          <t>VIRREY SOLIS IPS SA ALPES</t>
         </is>
       </c>
       <c r="D42">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="E42">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="F42">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>119</v>
+        <v>4</v>
       </c>
       <c r="I42">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>115</v>
+        <v>3</v>
+      </c>
+      <c r="L42">
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -1884,69 +1973,75 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA CERRITOS</t>
-        </is>
+          <t>VIRREY SOLIS IPS SA LA REBECA</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>89</v>
+      </c>
+      <c r="E43">
+        <v>93</v>
+      </c>
+      <c r="F43">
+        <v>95</v>
+      </c>
+      <c r="G43">
+        <v>44</v>
+      </c>
+      <c r="H43">
+        <v>119</v>
       </c>
       <c r="I43">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="J43">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="K43">
-        <v>18</v>
+        <v>115</v>
+      </c>
+      <c r="L43">
+        <v>90</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6600102793</t>
+          <t>6600102601</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>2</v>
-      </c>
-      <c r="F44">
-        <v>3</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
-      </c>
-      <c r="H44">
-        <v>6</v>
+          <t>VIRREY SOLIS IPS SA CERRITOS</t>
+        </is>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K44">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="L44">
+        <v>88</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6600102893</t>
+          <t>6600102793</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1956,38 +2051,41 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEUROMEDICA SAS</t>
+          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
         </is>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="L45">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6600103012</t>
+          <t>6600102893</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1997,35 +2095,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
+          <t>NEUROMEDICA SAS</t>
         </is>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>24</v>
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6600103078</t>
+          <t>6600103012</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2035,38 +2139,38 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
+          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
         </is>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>4</v>
-      </c>
-      <c r="F47">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H47">
+        <v>7</v>
+      </c>
+      <c r="I47">
+        <v>20</v>
+      </c>
+      <c r="J47">
+        <v>8</v>
+      </c>
+      <c r="K47">
+        <v>7</v>
+      </c>
+      <c r="L47">
         <v>6</v>
-      </c>
-      <c r="I47">
-        <v>2</v>
-      </c>
-      <c r="J47">
-        <v>3</v>
-      </c>
-      <c r="K47">
-        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6600103144</t>
+          <t>6600103078</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2076,38 +2180,41 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLINICA LOS NEVADOS SAS</t>
+          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
         </is>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="L48">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6600103334</t>
+          <t>6600103144</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2117,35 +2224,41 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CLINICA CENTRAL DEL EJE SAS</t>
+          <t>CLINICA LOS NEVADOS SAS</t>
         </is>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
         <v>3</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6600103414</t>
+          <t>6600103334</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2155,155 +2268,208 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CLINICA MEDICA TURIN SAS</t>
+          <t>CLINICA CENTRAL DEL EJE SAS</t>
         </is>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
       <c r="K50">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6600161600</t>
+          <t>6600103414</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EPMSC PEREIRA</t>
+          <t>CLINICA MEDICA TURIN SAS</t>
         </is>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6600171151</t>
+          <t>6600161600</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+          <t>EPMSC PEREIRA</t>
         </is>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F52">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G52">
         <v>16</v>
       </c>
       <c r="H52">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="I52">
-        <v>316</v>
+        <v>4</v>
       </c>
       <c r="J52">
         <v>9</v>
       </c>
       <c r="K52">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="L52">
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>6600171151</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53">
+        <v>29</v>
+      </c>
+      <c r="F53">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>16</v>
+      </c>
+      <c r="H53">
+        <v>88</v>
+      </c>
+      <c r="I53">
+        <v>316</v>
+      </c>
+      <c r="J53">
+        <v>9</v>
+      </c>
+      <c r="K53">
+        <v>13</v>
+      </c>
+      <c r="L53">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>6600183029</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>BATALLON SAN MATEO</t>
         </is>
       </c>
-      <c r="D53">
+      <c r="D54">
         <v>7</v>
       </c>
-      <c r="E53">
+      <c r="E54">
         <v>11</v>
       </c>
-      <c r="F53">
+      <c r="F54">
         <v>13</v>
       </c>
-      <c r="G53">
+      <c r="G54">
         <v>19</v>
       </c>
-      <c r="H53">
+      <c r="H54">
         <v>25</v>
       </c>
-      <c r="I53">
+      <c r="I54">
         <v>26</v>
       </c>
-      <c r="J53">
+      <c r="J54">
         <v>43</v>
       </c>
-      <c r="K53">
+      <c r="K54">
         <v>54</v>
+      </c>
+      <c r="L54">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -415,6 +415,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -476,9 +481,18 @@
           <t>INSTITUTO DE DIAGNOSTICO MEDICO SA</t>
         </is>
       </c>
+      <c r="D3">
+        <v>95</v>
+      </c>
       <c r="E3">
         <v>58</v>
       </c>
+      <c r="F3">
+        <v>57</v>
+      </c>
+      <c r="G3">
+        <v>53</v>
+      </c>
       <c r="H3">
         <v>95</v>
       </c>
@@ -494,6 +508,9 @@
       <c r="L3">
         <v>168</v>
       </c>
+      <c r="M3">
+        <v>92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -564,6 +581,9 @@
       <c r="L5">
         <v>2</v>
       </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,6 +628,9 @@
       <c r="L6">
         <v>966</v>
       </c>
+      <c r="M6">
+        <v>88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,6 +675,9 @@
       <c r="L7">
         <v>39</v>
       </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -696,6 +722,9 @@
       <c r="L8">
         <v>39</v>
       </c>
+      <c r="M8">
+        <v>44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -740,6 +769,9 @@
       <c r="L9">
         <v>2</v>
       </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -813,6 +845,9 @@
       <c r="L11">
         <v>1</v>
       </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -880,6 +915,9 @@
       <c r="L13">
         <v>1</v>
       </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -921,6 +959,9 @@
       <c r="L14">
         <v>1</v>
       </c>
+      <c r="M14">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -956,6 +997,9 @@
       <c r="L15">
         <v>2</v>
       </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -976,6 +1020,9 @@
       <c r="J16">
         <v>2</v>
       </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1107,6 +1154,9 @@
       <c r="L20">
         <v>6</v>
       </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1151,6 +1201,9 @@
       <c r="L21">
         <v>60</v>
       </c>
+      <c r="M21">
+        <v>42</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1180,6 +1233,9 @@
       <c r="I22">
         <v>5</v>
       </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1250,6 +1306,9 @@
       <c r="L24">
         <v>442</v>
       </c>
+      <c r="M24">
+        <v>308</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1273,6 +1332,9 @@
       <c r="L25">
         <v>594</v>
       </c>
+      <c r="M25">
+        <v>25</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1317,6 +1379,9 @@
       <c r="L26">
         <v>0</v>
       </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1405,6 +1470,9 @@
       <c r="L28">
         <v>12</v>
       </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1449,6 +1517,9 @@
       <c r="L29">
         <v>71</v>
       </c>
+      <c r="M29">
+        <v>39</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1493,6 +1564,9 @@
       <c r="L30">
         <v>56</v>
       </c>
+      <c r="M30">
+        <v>26</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1537,6 +1611,9 @@
       <c r="L31">
         <v>13</v>
       </c>
+      <c r="M31">
+        <v>12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1624,6 +1701,9 @@
       <c r="L34">
         <v>12</v>
       </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1700,6 +1780,9 @@
       <c r="L36">
         <v>20</v>
       </c>
+      <c r="M36">
+        <v>75</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1744,6 +1827,9 @@
       <c r="L37">
         <v>112</v>
       </c>
+      <c r="M37">
+        <v>54</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1788,6 +1874,9 @@
       <c r="L38">
         <v>11</v>
       </c>
+      <c r="M38">
+        <v>40</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1830,7 +1919,10 @@
         <v>182</v>
       </c>
       <c r="L39">
-        <v>194</v>
+        <v>388</v>
+      </c>
+      <c r="M39">
+        <v>183</v>
       </c>
     </row>
     <row r="40">
@@ -1876,6 +1968,9 @@
       <c r="L40">
         <v>63</v>
       </c>
+      <c r="M40">
+        <v>42</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1920,6 +2015,9 @@
       <c r="L41">
         <v>151</v>
       </c>
+      <c r="M41">
+        <v>150</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1964,6 +2062,9 @@
       <c r="L42">
         <v>48</v>
       </c>
+      <c r="M42">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2008,6 +2109,9 @@
       <c r="L43">
         <v>90</v>
       </c>
+      <c r="M43">
+        <v>258</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2037,6 +2141,9 @@
       <c r="L44">
         <v>88</v>
       </c>
+      <c r="M44">
+        <v>51</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2081,6 +2188,9 @@
       <c r="L45">
         <v>5</v>
       </c>
+      <c r="M45">
+        <v>6</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2125,6 +2235,9 @@
       <c r="L46">
         <v>0</v>
       </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2166,6 +2279,9 @@
       <c r="L47">
         <v>6</v>
       </c>
+      <c r="M47">
+        <v>7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2210,6 +2326,9 @@
       <c r="L48">
         <v>4</v>
       </c>
+      <c r="M48">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2254,6 +2373,9 @@
       <c r="L49">
         <v>3</v>
       </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2295,6 +2417,9 @@
       <c r="L50">
         <v>1</v>
       </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2339,6 +2464,9 @@
       <c r="L51">
         <v>0</v>
       </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2383,6 +2511,9 @@
       <c r="L52">
         <v>9</v>
       </c>
+      <c r="M52">
+        <v>12</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2425,7 +2556,10 @@
         <v>13</v>
       </c>
       <c r="L53">
-        <v>59</v>
+        <v>118</v>
+      </c>
+      <c r="M53">
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -2470,6 +2604,9 @@
       </c>
       <c r="L54">
         <v>31</v>
+      </c>
+      <c r="M54">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -420,6 +420,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,7 +466,7 @@
         <v>25</v>
       </c>
       <c r="J2">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="K2">
         <v>32</v>
@@ -464,6 +474,15 @@
       <c r="L2">
         <v>31</v>
       </c>
+      <c r="M2">
+        <v>60</v>
+      </c>
+      <c r="N2">
+        <v>39</v>
+      </c>
+      <c r="O2">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,17 +519,20 @@
         <v>86</v>
       </c>
       <c r="J3">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="K3">
         <v>82</v>
       </c>
       <c r="L3">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="M3">
         <v>92</v>
       </c>
+      <c r="N3">
+        <v>69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +559,12 @@
       <c r="K4">
         <v>0</v>
       </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -575,14 +603,17 @@
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
       <c r="L5">
         <v>2</v>
       </c>
       <c r="M5">
         <v>2</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -626,11 +657,17 @@
         <v>86</v>
       </c>
       <c r="L6">
-        <v>966</v>
+        <v>69</v>
       </c>
       <c r="M6">
         <v>88</v>
       </c>
+      <c r="N6">
+        <v>87</v>
+      </c>
+      <c r="O6">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +715,12 @@
       <c r="M7">
         <v>2</v>
       </c>
+      <c r="N7">
+        <v>27</v>
+      </c>
+      <c r="O7">
+        <v>31</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -725,6 +768,12 @@
       <c r="M8">
         <v>44</v>
       </c>
+      <c r="N8">
+        <v>24</v>
+      </c>
+      <c r="O8">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -848,6 +897,9 @@
       <c r="M11">
         <v>3</v>
       </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -875,7 +927,7 @@
         <v>3</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -918,6 +970,12 @@
       <c r="M13">
         <v>2</v>
       </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -962,6 +1020,9 @@
       <c r="M14">
         <v>4</v>
       </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1000,6 +1061,9 @@
       <c r="M15">
         <v>2</v>
       </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1058,6 +1122,9 @@
       <c r="L17">
         <v>2</v>
       </c>
+      <c r="N17">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1067,21 +1134,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD LA BELLA</t>
-        </is>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="K18">
+          <t>PUESTO DE SALUD CRUCERO DE COMBIA</t>
+        </is>
+      </c>
+      <c r="O18">
         <v>1</v>
       </c>
     </row>
@@ -1093,24 +1154,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ARABIA</t>
+          <t>PUESTO DE SALUD LA BELLA</t>
         </is>
       </c>
       <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
-      </c>
-      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="O19">
         <v>1</v>
       </c>
     </row>
@@ -1122,40 +1183,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ALTAGRACIA</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>4</v>
+          <t>PUESTO DE SALUD ARABIA</t>
+        </is>
       </c>
       <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
         <v>3</v>
       </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
       <c r="H20">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J20">
-        <v>7</v>
-      </c>
-      <c r="K20">
-        <v>6</v>
-      </c>
-      <c r="L20">
-        <v>6</v>
-      </c>
-      <c r="M20">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1166,43 +1218,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HOSPITAL DEL CENTRO</t>
+          <t>PUESTO DE SALUD ALTAGRACIA</t>
         </is>
       </c>
       <c r="D21">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>34</v>
-      </c>
-      <c r="I21">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1213,28 +1265,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD CASA DEL ABUELO</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-      <c r="I22">
-        <v>5</v>
-      </c>
-      <c r="M22">
-        <v>2</v>
+          <t>PUESTO DE SALUD MORELIA</t>
+        </is>
+      </c>
+      <c r="O22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1245,101 +1285,119 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD EL REMANSO</t>
-        </is>
+          <t>HOSPITAL DEL CENTRO</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>29</v>
+      </c>
+      <c r="E23">
+        <v>21</v>
+      </c>
+      <c r="F23">
+        <v>36</v>
+      </c>
+      <c r="G23">
+        <v>37</v>
+      </c>
+      <c r="H23">
+        <v>34</v>
+      </c>
+      <c r="I23">
+        <v>43</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="M23">
+        <v>42</v>
+      </c>
+      <c r="N23">
+        <v>33</v>
+      </c>
+      <c r="O23">
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6600100361</t>
+          <t>6600100332</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLINICA LOS ROSALES</t>
+          <t>CENTRO DE SALUD CASA DEL ABUELO</t>
         </is>
       </c>
       <c r="D24">
-        <v>184</v>
-      </c>
-      <c r="E24">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>146</v>
-      </c>
-      <c r="H24">
-        <v>171</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>174</v>
-      </c>
-      <c r="J24">
-        <v>386</v>
-      </c>
-      <c r="K24">
-        <v>214</v>
-      </c>
-      <c r="L24">
-        <v>442</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>308</v>
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6600100532</t>
+          <t>6600100332</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>QUIRÓFANO CASALUD SAS</t>
-        </is>
+          <t>CENTRO DE SALUD EL REMANSO</t>
+        </is>
+      </c>
+      <c r="J25">
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>594</v>
-      </c>
-      <c r="M25">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6600100663</t>
+          <t>6600100361</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1349,88 +1407,76 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ONCOLOGOS DEL OCCIDENTE SA</t>
+          <t>CLINICA LOS ROSALES</t>
         </is>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="N26">
+        <v>125</v>
+      </c>
+      <c r="O26">
+        <v>173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6600100762</t>
+          <t>6600100532</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ESE HOSPITAL UNIVERSITARIO SAN JORGE DE PEREIRA</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>29</v>
-      </c>
-      <c r="E27">
-        <v>42</v>
-      </c>
-      <c r="F27">
-        <v>48</v>
-      </c>
-      <c r="G27">
-        <v>58</v>
-      </c>
-      <c r="H27">
-        <v>47</v>
-      </c>
-      <c r="I27">
-        <v>54</v>
-      </c>
-      <c r="J27">
-        <v>94</v>
+          <t>QUIRÓFANO CASALUD SAS</t>
+        </is>
       </c>
       <c r="K27">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>51</v>
+        <v>297</v>
+      </c>
+      <c r="M27">
+        <v>25</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6600100785</t>
+          <t>6600100663</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1440,91 +1486,103 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FUNDACIÓN LA LIGA AMA SALVAR VIDAS</t>
+          <t>ONCOLOGOS DEL OCCIDENTE SA</t>
         </is>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6600101587</t>
+          <t>6600100762</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS Y SERVICIOS M</t>
+          <t>ESE HOSPITAL UNIVERSITARIO SAN JORGE DE PEREIRA</t>
         </is>
       </c>
       <c r="D29">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E29">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F29">
+        <v>48</v>
+      </c>
+      <c r="G29">
+        <v>58</v>
+      </c>
+      <c r="H29">
+        <v>47</v>
+      </c>
+      <c r="I29">
+        <v>54</v>
+      </c>
+      <c r="J29">
+        <v>47</v>
+      </c>
+      <c r="K29">
+        <v>66</v>
+      </c>
+      <c r="L29">
         <v>51</v>
       </c>
-      <c r="G29">
-        <v>35</v>
-      </c>
-      <c r="H29">
-        <v>40</v>
-      </c>
-      <c r="I29">
-        <v>34</v>
-      </c>
-      <c r="J29">
-        <v>68</v>
-      </c>
-      <c r="K29">
-        <v>43</v>
-      </c>
-      <c r="L29">
-        <v>71</v>
-      </c>
       <c r="M29">
-        <v>39</v>
+        <v>52</v>
+      </c>
+      <c r="N29">
+        <v>44</v>
+      </c>
+      <c r="O29">
+        <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6600101736</t>
+          <t>6600100785</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1534,91 +1592,103 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MEDICA SALUD PARA LOS COLOMBIANOS - CM</t>
+          <t>FUNDACIÓN LA LIGA AMA SALVAR VIDAS</t>
         </is>
       </c>
       <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>7</v>
+      </c>
+      <c r="H30">
         <v>4</v>
       </c>
-      <c r="E30">
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
         <v>3</v>
       </c>
-      <c r="F30">
-        <v>8</v>
-      </c>
-      <c r="G30">
-        <v>8</v>
-      </c>
-      <c r="H30">
-        <v>6</v>
-      </c>
-      <c r="I30">
-        <v>13</v>
-      </c>
-      <c r="J30">
-        <v>25</v>
-      </c>
-      <c r="K30">
-        <v>42</v>
-      </c>
       <c r="L30">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="M30">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6600101781</t>
+          <t>6600101587</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SINERGIA GLOBAL EN SALUD SAS</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS Y SERVICIOS M</t>
         </is>
       </c>
       <c r="D31">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="F31">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H31">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J31">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K31">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="L31">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="M31">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="N31">
+        <v>32</v>
+      </c>
+      <c r="O31">
+        <v>54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6600101912</t>
+          <t>6600101736</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1628,41 +1698,47 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RED MEDICA VITAL SAS</t>
+          <t>CORPORACIÓN MEDICA SALUD PARA LOS COLOMBIANOS - CM</t>
         </is>
       </c>
       <c r="D32">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H32">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="I32">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="J32">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="K32">
-        <v>110</v>
-      </c>
-      <c r="L32">
-        <v>51</v>
+        <v>42</v>
+      </c>
+      <c r="M32">
+        <v>26</v>
+      </c>
+      <c r="N32">
+        <v>23</v>
+      </c>
+      <c r="O32">
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6600102288</t>
+          <t>6600101781</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1672,122 +1748,149 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SALUD PYP SAS</t>
-        </is>
+          <t>SINERGIA GLOBAL EN SALUD SAS</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>19</v>
+      </c>
+      <c r="E33">
+        <v>7</v>
+      </c>
+      <c r="F33">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+      <c r="I33">
+        <v>10</v>
+      </c>
+      <c r="J33">
+        <v>13</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="L33">
+        <v>13</v>
+      </c>
+      <c r="M33">
+        <v>12</v>
+      </c>
+      <c r="N33">
+        <v>9</v>
+      </c>
+      <c r="O33">
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6600102402</t>
+          <t>6600101912</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
-        </is>
+          <t>RED MEDICA VITAL SAS</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>78</v>
+      </c>
+      <c r="E34">
+        <v>60</v>
+      </c>
+      <c r="F34">
+        <v>49</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>45</v>
+      </c>
+      <c r="H34">
+        <v>34</v>
+      </c>
+      <c r="I34">
+        <v>59</v>
+      </c>
+      <c r="J34">
+        <v>71</v>
+      </c>
+      <c r="K34">
+        <v>55</v>
       </c>
       <c r="L34">
-        <v>12</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6600102411</t>
+          <t>6600102288</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
-        </is>
-      </c>
-      <c r="F35">
-        <v>5</v>
-      </c>
-      <c r="H35">
-        <v>9</v>
-      </c>
-      <c r="I35">
-        <v>11</v>
-      </c>
-      <c r="J35">
-        <v>18</v>
-      </c>
-      <c r="L35">
-        <v>14</v>
+          <t>SALUD PYP SAS</t>
+        </is>
+      </c>
+      <c r="K35">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6600102446</t>
+          <t>6600102402</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>108</v>
-      </c>
-      <c r="E36">
-        <v>61</v>
-      </c>
-      <c r="F36">
-        <v>123</v>
+          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
+        </is>
       </c>
       <c r="G36">
-        <v>67</v>
-      </c>
-      <c r="H36">
-        <v>99</v>
-      </c>
-      <c r="I36">
-        <v>71</v>
-      </c>
-      <c r="J36">
-        <v>97</v>
-      </c>
-      <c r="K36">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="L36">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6600102446</t>
+          <t>6600102411</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1797,226 +1900,235 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>65</v>
-      </c>
-      <c r="E37">
-        <v>57</v>
+          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
+        </is>
       </c>
       <c r="F37">
-        <v>48</v>
-      </c>
-      <c r="G37">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H37">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="J37">
-        <v>44</v>
-      </c>
-      <c r="K37">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>112</v>
-      </c>
-      <c r="M37">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6600102453</t>
+          <t>6600102446</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VITALCARE IPS SAS</t>
+          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
         </is>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="E38">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F38">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="H38">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="I38">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="J38">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="K38">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="L38">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M38">
-        <v>40</v>
+        <v>75</v>
+      </c>
+      <c r="N38">
+        <v>56</v>
+      </c>
+      <c r="O38">
+        <v>48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6600102477</t>
+          <t>6600102446</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
+          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
         </is>
       </c>
       <c r="D39">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="E39">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="F39">
-        <v>169</v>
+        <v>48</v>
       </c>
       <c r="G39">
-        <v>168</v>
+        <v>42</v>
       </c>
       <c r="H39">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="I39">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="J39">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="K39">
-        <v>182</v>
+        <v>57</v>
       </c>
       <c r="L39">
-        <v>388</v>
+        <v>56</v>
       </c>
       <c r="M39">
-        <v>183</v>
+        <v>54</v>
+      </c>
+      <c r="N39">
+        <v>48</v>
+      </c>
+      <c r="O39">
+        <v>44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6600102601</t>
+          <t>6600102453</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS SA PINARES</t>
+          <t>VITALCARE IPS SAS</t>
         </is>
       </c>
       <c r="D40">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="E40">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F40">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="G40">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="H40">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="I40">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="J40">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="K40">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="L40">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="M40">
-        <v>42</v>
+        <v>20</v>
+      </c>
+      <c r="N40">
+        <v>31</v>
+      </c>
+      <c r="O40">
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6600102601</t>
+          <t>6600102477</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS LAGO</t>
+          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
         </is>
       </c>
       <c r="D41">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="E41">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="F41">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="H41">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="I41">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="J41">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="K41">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L41">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="M41">
-        <v>150</v>
+        <v>183</v>
+      </c>
+      <c r="N41">
+        <v>177</v>
+      </c>
+      <c r="O41">
+        <v>167</v>
       </c>
     </row>
     <row r="42">
@@ -2027,43 +2139,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA ALPES</t>
+          <t>VIRREY SOLIS SA PINARES</t>
         </is>
       </c>
       <c r="D42">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="E42">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="L42">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="N42">
+        <v>59</v>
+      </c>
+      <c r="O42">
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -2074,43 +2192,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA LA REBECA</t>
+          <t>VIRREY SOLIS IPS LAGO</t>
         </is>
       </c>
       <c r="D43">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="E43">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="F43">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="G43">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="H43">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I43">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="J43">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="K43">
+        <v>165</v>
+      </c>
+      <c r="L43">
+        <v>151</v>
+      </c>
+      <c r="M43">
+        <v>150</v>
+      </c>
+      <c r="N43">
+        <v>122</v>
+      </c>
+      <c r="O43">
         <v>115</v>
-      </c>
-      <c r="L43">
-        <v>90</v>
-      </c>
-      <c r="M43">
-        <v>258</v>
       </c>
     </row>
     <row r="44">
@@ -2121,128 +2245,146 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA CERRITOS</t>
-        </is>
+          <t>VIRREY SOLIS IPS SA ALPES</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>9</v>
+      </c>
+      <c r="E44">
+        <v>9</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J44">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="M44">
-        <v>51</v>
+        <v>3</v>
+      </c>
+      <c r="N44">
+        <v>10</v>
+      </c>
+      <c r="O44">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6600102793</t>
+          <t>6600102601</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
+          <t>VIRREY SOLIS IPS SA LA REBECA</t>
         </is>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H45">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="K45">
-        <v>2</v>
+        <v>115</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>129</v>
+      </c>
+      <c r="N45">
+        <v>81</v>
+      </c>
+      <c r="O45">
+        <v>95</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6600102893</t>
+          <t>6600102601</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEUROMEDICA SAS</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
+          <t>VIRREY SOLIS IPS SA CERRITOS</t>
+        </is>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="N46">
+        <v>51</v>
+      </c>
+      <c r="O46">
+        <v>39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6600103012</t>
+          <t>6600102793</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2252,41 +2394,50 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
+          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
         </is>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>24</v>
+        <v>2</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
       </c>
       <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
         <v>6</v>
       </c>
-      <c r="H47">
-        <v>7</v>
-      </c>
       <c r="I47">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L47">
+        <v>5</v>
+      </c>
+      <c r="M47">
         <v>6</v>
       </c>
-      <c r="M47">
-        <v>7</v>
+      <c r="N47">
+        <v>2</v>
+      </c>
+      <c r="O47">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6600103078</t>
+          <t>6600102893</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2296,44 +2447,50 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
+          <t>NEUROMEDICA SAS</t>
         </is>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6600103144</t>
+          <t>6600103012</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2343,44 +2500,47 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CLINICA LOS NEVADOS SAS</t>
+          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
         </is>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L49">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="N49">
+        <v>5</v>
+      </c>
+      <c r="O49">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6600103334</t>
+          <t>6600103078</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2390,41 +2550,50 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CLINICA CENTRAL DEL EJE SAS</t>
+          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
         </is>
       </c>
       <c r="D50">
+        <v>9</v>
+      </c>
+      <c r="E50">
         <v>4</v>
       </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
       <c r="F50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H50">
+        <v>6</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
         <v>3</v>
       </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
       <c r="K50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="N50">
+        <v>3</v>
+      </c>
+      <c r="O50">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6600103414</t>
+          <t>6600103144</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2434,14 +2603,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CLINICA MEDICA TURIN SAS</t>
+          <t>CLINICA LOS NEVADOS SAS</t>
         </is>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -2456,69 +2625,81 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M51">
         <v>0</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6600161600</t>
+          <t>6600103334</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EPMSC PEREIRA</t>
+          <t>CLINICA CENTRAL DEL EJE SAS</t>
         </is>
       </c>
       <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52">
         <v>3</v>
       </c>
-      <c r="E52">
-        <v>8</v>
-      </c>
-      <c r="F52">
-        <v>7</v>
-      </c>
-      <c r="G52">
-        <v>16</v>
-      </c>
-      <c r="H52">
-        <v>10</v>
-      </c>
       <c r="I52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L52">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M52">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6600171151</t>
+          <t>6600103414</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2528,85 +2709,200 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+          <t>CLINICA MEDICA TURIN SAS</t>
         </is>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>6600161600</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EPMSC PEREIRA</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>8</v>
+      </c>
+      <c r="F54">
+        <v>7</v>
+      </c>
+      <c r="G54">
+        <v>16</v>
+      </c>
+      <c r="H54">
+        <v>10</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
+      </c>
+      <c r="J54">
+        <v>9</v>
+      </c>
+      <c r="K54">
+        <v>5</v>
+      </c>
+      <c r="L54">
+        <v>9</v>
+      </c>
+      <c r="M54">
+        <v>12</v>
+      </c>
+      <c r="N54">
+        <v>12</v>
+      </c>
+      <c r="O54">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>6600171151</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55">
+        <v>29</v>
+      </c>
+      <c r="F55">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>16</v>
+      </c>
+      <c r="H55">
+        <v>88</v>
+      </c>
+      <c r="I55">
+        <v>158</v>
+      </c>
+      <c r="J55">
+        <v>9</v>
+      </c>
+      <c r="K55">
+        <v>13</v>
+      </c>
+      <c r="L55">
+        <v>59</v>
+      </c>
+      <c r="M55">
+        <v>15</v>
+      </c>
+      <c r="N55">
+        <v>71</v>
+      </c>
+      <c r="O55">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>6600183029</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>BATALLON SAN MATEO</t>
         </is>
       </c>
-      <c r="D54">
+      <c r="D56">
         <v>7</v>
       </c>
-      <c r="E54">
+      <c r="E56">
         <v>11</v>
       </c>
-      <c r="F54">
+      <c r="F56">
         <v>13</v>
       </c>
-      <c r="G54">
+      <c r="G56">
         <v>19</v>
       </c>
-      <c r="H54">
-        <v>25</v>
-      </c>
-      <c r="I54">
+      <c r="I56">
         <v>26</v>
       </c>
-      <c r="J54">
+      <c r="J56">
         <v>43</v>
       </c>
-      <c r="K54">
+      <c r="K56">
         <v>54</v>
       </c>
-      <c r="L54">
+      <c r="L56">
         <v>31</v>
       </c>
-      <c r="M54">
+      <c r="M56">
         <v>18</v>
+      </c>
+      <c r="N56">
+        <v>21</v>
+      </c>
+      <c r="O56">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,60 +372,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -439,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -448,40 +453,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>44</v>
-      </c>
-      <c r="E2">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>33</v>
-      </c>
-      <c r="G2">
-        <v>16</v>
-      </c>
-      <c r="H2">
-        <v>20</v>
-      </c>
-      <c r="I2">
-        <v>25</v>
-      </c>
-      <c r="J2">
-        <v>41</v>
-      </c>
-      <c r="K2">
-        <v>32</v>
-      </c>
-      <c r="L2">
-        <v>31</v>
-      </c>
-      <c r="M2">
-        <v>60</v>
-      </c>
-      <c r="N2">
-        <v>39</v>
-      </c>
-      <c r="O2">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,70 +472,94 @@
           <t>INSTITUTO DE DIAGNOSTICO MEDICO SA</t>
         </is>
       </c>
-      <c r="D3">
-        <v>95</v>
-      </c>
       <c r="E3">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="I3">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="J3">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="K3">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="L3">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="M3">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="N3">
-        <v>69</v>
+        <v>60</v>
+      </c>
+      <c r="O3">
+        <v>39</v>
+      </c>
+      <c r="P3">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6600100217</t>
+          <t>6600100208</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO N° 1</t>
-        </is>
+          <t>INSTITUTO DE DIAGNOSTICO MEDICO SA</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>95</v>
+      </c>
+      <c r="F4">
+        <v>58</v>
+      </c>
+      <c r="G4">
+        <v>57</v>
+      </c>
+      <c r="H4">
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="L4">
+        <v>82</v>
+      </c>
+      <c r="M4">
+        <v>84</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
@@ -574,46 +570,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CAJA DE COMPENSACION FAMILIAR DE RISARALDA COMFAMI</t>
+          <t>CENTRO MEDICO N° 1</t>
         </is>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-      <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -624,7 +605,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -633,93 +614,96 @@
         </is>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>119</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>86</v>
-      </c>
-      <c r="L6">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>77</v>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6600100332</t>
+          <t>6600100217</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNIDAD INTERMEDIA DE KENNEDY</t>
+          <t>CAJA DE COMPENSACION FAMILIAR DE RISARALDA COMFAMI</t>
         </is>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="H7">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="J7">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="K7">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="N7">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="O7">
-        <v>31</v>
+        <v>87</v>
+      </c>
+      <c r="P7">
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -730,49 +714,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNIDAD INTERMEDIA DE CUBA</t>
+          <t>UNIDAD INTERMEDIA DE KENNEDY</t>
         </is>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K8">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L8">
+        <v>34</v>
+      </c>
+      <c r="M8">
         <v>39</v>
       </c>
-      <c r="M8">
-        <v>44</v>
-      </c>
       <c r="N8">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="P8">
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -783,43 +770,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD BOSTON</t>
+          <t>UNIDAD INTERMEDIA DE CUBA</t>
         </is>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="N9">
+        <v>44</v>
+      </c>
+      <c r="O9">
+        <v>24</v>
+      </c>
+      <c r="P9">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -830,36 +826,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD SANTA TERESITA</t>
+          <t>CENTRO DE SALUD BOSTON</t>
         </is>
       </c>
       <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
         <v>4</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
         <v>3</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-      <c r="K10">
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
         <v>1</v>
       </c>
     </row>
@@ -871,33 +876,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD SAN NICOLAS</t>
-        </is>
+          <t>CENTRO DE SALUD SANTA TERESITA</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
         <v>4</v>
       </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
       <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
-      <c r="O11">
         <v>1</v>
       </c>
     </row>
@@ -909,24 +920,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD SAN CAMILO</t>
-        </is>
-      </c>
-      <c r="G12">
+          <t>CENTRO DE SALUD SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="I12">
         <v>2</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
         <v>3</v>
       </c>
-      <c r="L12">
+      <c r="P12">
         <v>1</v>
       </c>
     </row>
@@ -938,42 +958,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD VILLASANTANA</t>
-        </is>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
+          <t>CENTRO DE SALUD SAN CAMILO</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13">
-        <v>2</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
         <v>1</v>
       </c>
     </row>
@@ -985,43 +987,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD PERLA DEL OTUN</t>
+          <t>CENTRO DE SALUD VILLASANTANA</t>
         </is>
       </c>
       <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>2</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1032,37 +1037,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD VILLA CONSOTA</t>
-        </is>
+          <t>CENTRO DE SALUD PERLA DEL OTUN</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>9</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
         <v>4</v>
       </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="L15">
-        <v>2</v>
-      </c>
-      <c r="M15">
-        <v>2</v>
-      </c>
-      <c r="N15">
-        <v>2</v>
+      <c r="O15">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1073,19 +1087,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD PUERTO CALDAS</t>
-        </is>
+          <t>CENTRO DE SALUD VILLA CONSOTA</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
       </c>
       <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
         <v>2</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1096,34 +1131,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CAIMALITO</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>4</v>
-      </c>
-      <c r="H17">
-        <v>4</v>
-      </c>
-      <c r="I17">
-        <v>3</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
+          <t>PUESTO DE SALUD PUERTO CALDAS</t>
+        </is>
       </c>
       <c r="K17">
         <v>2</v>
       </c>
-      <c r="L17">
-        <v>2</v>
-      </c>
       <c r="N17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1134,16 +1154,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CRUCERO DE COMBIA</t>
-        </is>
+          <t>PUESTO DE SALUD CAIMALITO</t>
+        </is>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1154,24 +1192,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD LA BELLA</t>
-        </is>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="O19">
+          <t>PUESTO DE SALUD CRUCERO DE COMBIA</t>
+        </is>
+      </c>
+      <c r="P19">
         <v>1</v>
       </c>
     </row>
@@ -1183,30 +1212,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ARABIA</t>
-        </is>
-      </c>
-      <c r="F20">
-        <v>2</v>
+          <t>PUESTO DE SALUD LA BELLA</t>
+        </is>
       </c>
       <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="P20">
         <v>1</v>
       </c>
     </row>
@@ -1218,43 +1241,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ALTAGRACIA</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21">
+          <t>PUESTO DE SALUD ARABIA</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
         <v>3</v>
       </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>10</v>
-      </c>
-      <c r="J21">
-        <v>7</v>
+      <c r="I21">
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>6</v>
-      </c>
-      <c r="L21">
-        <v>6</v>
-      </c>
-      <c r="M21">
-        <v>3</v>
-      </c>
-      <c r="N21">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1265,16 +1276,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MORELIA</t>
-        </is>
+          <t>PUESTO DE SALUD ALTAGRACIA</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="K22">
+        <v>7</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="M22">
+        <v>6</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1285,49 +1326,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HOSPITAL DEL CENTRO</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>29</v>
-      </c>
-      <c r="E23">
-        <v>21</v>
-      </c>
-      <c r="F23">
-        <v>36</v>
-      </c>
-      <c r="G23">
-        <v>37</v>
-      </c>
-      <c r="H23">
-        <v>34</v>
-      </c>
-      <c r="I23">
-        <v>43</v>
-      </c>
-      <c r="J23">
-        <v>47</v>
-      </c>
-      <c r="K23">
-        <v>45</v>
-      </c>
-      <c r="L23">
-        <v>60</v>
-      </c>
-      <c r="M23">
-        <v>42</v>
-      </c>
-      <c r="N23">
-        <v>33</v>
-      </c>
-      <c r="O23">
-        <v>36</v>
+          <t>PUESTO DE SALUD MORELIA</t>
+        </is>
+      </c>
+      <c r="P23">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1338,31 +1346,52 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD CASA DEL ABUELO</t>
+          <t>HOSPITAL DEL CENTRO</t>
         </is>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="E24">
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>36</v>
+      </c>
+      <c r="H24">
+        <v>37</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="J24">
+        <v>43</v>
+      </c>
+      <c r="K24">
+        <v>47</v>
+      </c>
+      <c r="L24">
+        <v>45</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="N24">
+        <v>42</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="P24">
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -1373,163 +1402,154 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD EL REMANSO</t>
-        </is>
+          <t>CENTRO DE SALUD CASA DEL ABUELO</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
-        <v>2</v>
-      </c>
-      <c r="L25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="P25">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6600100361</t>
+          <t>6600100332</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLINICA LOS ROSALES</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>184</v>
-      </c>
-      <c r="E26">
-        <v>119</v>
-      </c>
-      <c r="F26">
-        <v>143</v>
-      </c>
-      <c r="G26">
-        <v>146</v>
-      </c>
-      <c r="H26">
-        <v>171</v>
-      </c>
-      <c r="I26">
-        <v>174</v>
+          <t>CENTRO DE SALUD EL REMANSO</t>
+        </is>
       </c>
       <c r="K26">
-        <v>214</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>416</v>
+        <v>2</v>
       </c>
       <c r="M26">
-        <v>154</v>
-      </c>
-      <c r="N26">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6600100532</t>
+          <t>6600100361</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>QUIRÓFANO CASALUD SAS</t>
-        </is>
-      </c>
-      <c r="K27">
-        <v>0</v>
+          <t>CLINICA LOS ROSALES</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>104</v>
+      </c>
+      <c r="E27">
+        <v>184</v>
+      </c>
+      <c r="F27">
+        <v>119</v>
+      </c>
+      <c r="G27">
+        <v>143</v>
+      </c>
+      <c r="H27">
+        <v>146</v>
+      </c>
+      <c r="I27">
+        <v>171</v>
+      </c>
+      <c r="J27">
+        <v>174</v>
       </c>
       <c r="L27">
-        <v>297</v>
+        <v>214</v>
       </c>
       <c r="M27">
-        <v>25</v>
+        <v>416</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>154</v>
+      </c>
+      <c r="O27">
+        <v>125</v>
+      </c>
+      <c r="P27">
+        <v>173</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6600100663</t>
+          <t>6600100532</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ONCOLOGOS DEL OCCIDENTE SA</t>
+          <t>QUIRÓFANO CASALUD SAS</t>
         </is>
       </c>
       <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P28">
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6600100762</t>
+          <t>6600100663</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1539,50 +1559,53 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ESE HOSPITAL UNIVERSITARIO SAN JORGE DE PEREIRA</t>
+          <t>ONCOLOGOS DEL OCCIDENTE SA</t>
         </is>
       </c>
       <c r="D29">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>36</v>
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6600100785</t>
+          <t>6600100762</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1592,153 +1615,162 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FUNDACIÓN LA LIGA AMA SALVAR VIDAS</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>2</v>
+          <t>ESE HOSPITAL UNIVERSITARIO SAN JORGE DE PEREIRA</t>
+        </is>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="K30">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="L30">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="P30">
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6600101587</t>
+          <t>6600100785</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS Y SERVICIOS M</t>
+          <t>FUNDACIÓN LA LIGA AMA SALVAR VIDAS</t>
         </is>
       </c>
       <c r="D31">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I31">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="N31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6600101736</t>
+          <t>6600101587</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MEDICA SALUD PARA LOS COLOMBIANOS - CM</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS Y SERVICIOS M</t>
         </is>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="I32">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J32">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K32">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="L32">
+        <v>43</v>
       </c>
       <c r="M32">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="N32">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="O32">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="P32">
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6600101781</t>
+          <t>6600101736</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1748,47 +1780,50 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SINERGIA GLOBAL EN SALUD SAS</t>
+          <t>CORPORACIÓN MEDICA SALUD PARA LOS COLOMBIANOS - CM</t>
         </is>
       </c>
       <c r="D33">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>8</v>
       </c>
       <c r="I33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>13</v>
       </c>
       <c r="K33">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L33">
-        <v>13</v>
-      </c>
-      <c r="M33">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="N33">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="O33">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="P33">
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6600101912</t>
+          <t>6600101781</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1798,47 +1833,50 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RED MEDICA VITAL SAS</t>
+          <t>SINERGIA GLOBAL EN SALUD SAS</t>
         </is>
       </c>
       <c r="D34">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H34">
-        <v>34</v>
-      </c>
-      <c r="I34">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="L34">
-        <v>51</v>
+        <v>11</v>
+      </c>
+      <c r="M34">
+        <v>13</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O34">
-        <v>45</v>
+        <v>9</v>
+      </c>
+      <c r="P34">
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6600102288</t>
+          <t>6600101912</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1848,128 +1886,131 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SALUD PYP SAS</t>
-        </is>
+          <t>RED MEDICA VITAL SAS</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>40</v>
+      </c>
+      <c r="E35">
+        <v>78</v>
+      </c>
+      <c r="F35">
+        <v>60</v>
+      </c>
+      <c r="G35">
+        <v>49</v>
+      </c>
+      <c r="H35">
+        <v>45</v>
+      </c>
+      <c r="I35">
+        <v>34</v>
+      </c>
+      <c r="J35">
+        <v>59</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="L35">
+        <v>55</v>
+      </c>
+      <c r="M35">
+        <v>51</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6600102402</t>
+          <t>6600102288</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>2</v>
+          <t>SALUD PYP SAS</t>
+        </is>
       </c>
       <c r="L36">
-        <v>6</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36">
-        <v>1</v>
-      </c>
-      <c r="O36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6600102411</t>
+          <t>6600102402</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
-        </is>
-      </c>
-      <c r="F37">
-        <v>5</v>
+          <t>IPS CENTRO DE MEDICINA INTEGRATIVA SAS</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>9</v>
-      </c>
-      <c r="I37">
-        <v>11</v>
-      </c>
-      <c r="J37">
-        <v>9</v>
-      </c>
-      <c r="L37">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="M37">
+        <v>6</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6600102446</t>
+          <t>6600102411</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>108</v>
-      </c>
-      <c r="E38">
-        <v>61</v>
-      </c>
-      <c r="F38">
-        <v>123</v>
+          <t>SERVICIOS DE SALUD IPS SURAMERICANA SA</t>
+        </is>
       </c>
       <c r="G38">
-        <v>67</v>
-      </c>
-      <c r="H38">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="I38">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="K38">
-        <v>98</v>
-      </c>
-      <c r="L38">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>75</v>
-      </c>
-      <c r="N38">
-        <v>56</v>
-      </c>
-      <c r="O38">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1980,7 +2021,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1989,46 +2030,49 @@
         </is>
       </c>
       <c r="D39">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E39">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F39">
+        <v>61</v>
+      </c>
+      <c r="G39">
+        <v>123</v>
+      </c>
+      <c r="H39">
+        <v>67</v>
+      </c>
+      <c r="I39">
+        <v>99</v>
+      </c>
+      <c r="J39">
+        <v>71</v>
+      </c>
+      <c r="K39">
+        <v>97</v>
+      </c>
+      <c r="L39">
+        <v>98</v>
+      </c>
+      <c r="M39">
+        <v>20</v>
+      </c>
+      <c r="N39">
+        <v>75</v>
+      </c>
+      <c r="O39">
+        <v>56</v>
+      </c>
+      <c r="P39">
         <v>48</v>
-      </c>
-      <c r="G39">
-        <v>42</v>
-      </c>
-      <c r="H39">
-        <v>48</v>
-      </c>
-      <c r="I39">
-        <v>39</v>
-      </c>
-      <c r="J39">
-        <v>44</v>
-      </c>
-      <c r="K39">
-        <v>57</v>
-      </c>
-      <c r="L39">
-        <v>56</v>
-      </c>
-      <c r="M39">
-        <v>54</v>
-      </c>
-      <c r="N39">
-        <v>48</v>
-      </c>
-      <c r="O39">
-        <v>44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6600102453</t>
+          <t>6600102446</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2038,103 +2082,109 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VITALCARE IPS SAS</t>
+          <t>CAJA COLOMBIANA DE SUBSIDIO FAMILIAR COLSUBSIDIO</t>
         </is>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F40">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H40">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="I40">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J40">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K40">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L40">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="M40">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="N40">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="O40">
-        <v>18</v>
+        <v>48</v>
+      </c>
+      <c r="P40">
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6600102477</t>
+          <t>6600102453</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
+          <t>VITALCARE IPS SAS</t>
         </is>
       </c>
       <c r="D41">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="E41">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="F41">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="G41">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="H41">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="K41">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="L41">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="M41">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="N41">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="O41">
-        <v>167</v>
+        <v>31</v>
+      </c>
+      <c r="P41">
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6600102601</t>
+          <t>6600102477</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2144,44 +2194,47 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS SA PINARES</t>
+          <t>EMPRESA DE MEDICINA INTEGRAL EMI SA - SERVICIO DE</t>
         </is>
       </c>
       <c r="D42">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="E42">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="F42">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="G42">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="H42">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="I42">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="J42">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="K42">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="L42">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="M42">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="N42">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="O42">
-        <v>30</v>
+        <v>177</v>
+      </c>
+      <c r="P42">
+        <v>167</v>
       </c>
     </row>
     <row r="43">
@@ -2192,49 +2245,52 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS LAGO</t>
+          <t>VIRREY SOLIS SA PINARES</t>
         </is>
       </c>
       <c r="D43">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="E43">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="F43">
-        <v>188</v>
+        <v>83</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="H43">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="I43">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="J43">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="K43">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="L43">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="M43">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="N43">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="O43">
-        <v>115</v>
+        <v>59</v>
+      </c>
+      <c r="P43">
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -2245,49 +2301,52 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA ALPES</t>
+          <t>VIRREY SOLIS IPS LAGO</t>
         </is>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="I44">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="J44">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="K44">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="L44">
-        <v>4</v>
+        <v>165</v>
       </c>
       <c r="M44">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="N44">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="O44">
-        <v>5</v>
+        <v>122</v>
+      </c>
+      <c r="P44">
+        <v>115</v>
       </c>
     </row>
     <row r="45">
@@ -2298,49 +2357,52 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA LA REBECA</t>
+          <t>VIRREY SOLIS IPS SA ALPES</t>
         </is>
       </c>
       <c r="D45">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="F45">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="G45">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="J45">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="L45">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="M45">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="N45">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="O45">
-        <v>95</v>
+        <v>10</v>
+      </c>
+      <c r="P45">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -2351,93 +2413,99 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VIRREY SOLIS IPS SA CERRITOS</t>
-        </is>
+          <t>VIRREY SOLIS IPS SA LA REBECA</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>64</v>
+      </c>
+      <c r="E46">
+        <v>89</v>
+      </c>
+      <c r="F46">
+        <v>93</v>
+      </c>
+      <c r="G46">
+        <v>95</v>
+      </c>
+      <c r="H46">
+        <v>44</v>
       </c>
       <c r="I46">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="J46">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="K46">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="L46">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="M46">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N46">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="O46">
-        <v>39</v>
+        <v>81</v>
+      </c>
+      <c r="P46">
+        <v>95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6600102793</t>
+          <t>6600102601</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
+          <t>VIRREY SOLIS IPS SA CERRITOS</t>
         </is>
       </c>
       <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
-      <c r="G47">
-        <v>2</v>
-      </c>
-      <c r="H47">
-        <v>6</v>
-      </c>
-      <c r="I47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K47">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="P47">
+        <v>39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6600102893</t>
+          <t>6600102793</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2447,50 +2515,53 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NEUROMEDICA SAS</t>
+          <t>CENTRO MEDICO PEREIRA COLSANITAS</t>
         </is>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P48">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6600103012</t>
+          <t>6600102893</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2500,47 +2571,53 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
+          <t>NEUROMEDICA SAS</t>
         </is>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6600103078</t>
+          <t>6600103012</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2550,50 +2627,50 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
+          <t>SPORT MEDICAL IPS GUSTAVO PORTELA SAS</t>
         </is>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F50">
-        <v>3</v>
-      </c>
-      <c r="G50">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H50">
         <v>6</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K50">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O50">
+        <v>5</v>
+      </c>
+      <c r="P50">
         <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6600103144</t>
+          <t>6600103078</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2603,50 +2680,50 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CLINICA LOS NEVADOS SAS</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>11</v>
+          <t>COOMEVA EXPERIENCIA MEDICA SAS</t>
+        </is>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51">
+        <v>4</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="N51">
         <v>3</v>
       </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>1</v>
-      </c>
       <c r="O51">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="P51">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6600103334</t>
+          <t>6600103144</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2656,50 +2733,53 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CLINICA CENTRAL DEL EJE SAS</t>
+          <t>CLINICA LOS NEVADOS SAS</t>
         </is>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>3</v>
       </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>1</v>
-      </c>
-      <c r="K52">
-        <v>3</v>
-      </c>
-      <c r="L52">
-        <v>1</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
       <c r="N52">
         <v>0</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P52">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6600103414</t>
+          <t>6600103334</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2709,199 +2789,264 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CLINICA MEDICA TURIN SAS</t>
+          <t>CLINICA CENTRAL DEL EJE SAS</t>
         </is>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6600161600</t>
+          <t>6600103414</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EPMSC PEREIRA</t>
+          <t>CLINICA MEDICA TURIN SAS</t>
         </is>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6600171151</t>
+          <t>6600161600</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+          <t>EPMSC PEREIRA</t>
         </is>
       </c>
       <c r="D55">
+        <v>8</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+      <c r="G55">
+        <v>7</v>
+      </c>
+      <c r="H55">
+        <v>16</v>
+      </c>
+      <c r="I55">
         <v>10</v>
       </c>
-      <c r="E55">
-        <v>29</v>
-      </c>
-      <c r="F55">
-        <v>11</v>
-      </c>
-      <c r="G55">
-        <v>16</v>
-      </c>
-      <c r="H55">
-        <v>88</v>
-      </c>
-      <c r="I55">
-        <v>158</v>
-      </c>
       <c r="J55">
+        <v>4</v>
+      </c>
+      <c r="K55">
         <v>9</v>
       </c>
-      <c r="K55">
-        <v>13</v>
-      </c>
       <c r="L55">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="M55">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N55">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="O55">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="P55">
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>6600171151</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>29</v>
+      </c>
+      <c r="G56">
+        <v>11</v>
+      </c>
+      <c r="H56">
+        <v>16</v>
+      </c>
+      <c r="I56">
+        <v>88</v>
+      </c>
+      <c r="J56">
+        <v>158</v>
+      </c>
+      <c r="K56">
+        <v>9</v>
+      </c>
+      <c r="L56">
+        <v>13</v>
+      </c>
+      <c r="M56">
+        <v>59</v>
+      </c>
+      <c r="N56">
+        <v>15</v>
+      </c>
+      <c r="O56">
+        <v>71</v>
+      </c>
+      <c r="P56">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>6600183029</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>BATALLON SAN MATEO</t>
         </is>
       </c>
-      <c r="D56">
+      <c r="D57">
+        <v>16</v>
+      </c>
+      <c r="E57">
         <v>7</v>
       </c>
-      <c r="E56">
+      <c r="F57">
         <v>11</v>
       </c>
-      <c r="F56">
+      <c r="G57">
         <v>13</v>
       </c>
-      <c r="G56">
+      <c r="H57">
         <v>19</v>
       </c>
-      <c r="I56">
+      <c r="J57">
         <v>26</v>
       </c>
-      <c r="J56">
+      <c r="K57">
         <v>43</v>
       </c>
-      <c r="K56">
+      <c r="L57">
         <v>54</v>
       </c>
-      <c r="L56">
+      <c r="M57">
         <v>31</v>
       </c>
-      <c r="M56">
+      <c r="N57">
         <v>18</v>
       </c>
-      <c r="N56">
+      <c r="O57">
         <v>21</v>
       </c>
-      <c r="O56">
+      <c r="P57">
         <v>26</v>
       </c>
     </row>

--- a/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -435,6 +435,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,6 +513,9 @@
       <c r="P3">
         <v>28</v>
       </c>
+      <c r="Q3">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -561,6 +569,9 @@
       <c r="O4">
         <v>69</v>
       </c>
+      <c r="Q4">
+        <v>46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -649,6 +660,9 @@
       <c r="P6">
         <v>4</v>
       </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -705,6 +719,9 @@
       <c r="P7">
         <v>77</v>
       </c>
+      <c r="Q7">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -761,6 +778,9 @@
       <c r="P8">
         <v>31</v>
       </c>
+      <c r="Q8">
+        <v>26</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -817,6 +837,9 @@
       <c r="P9">
         <v>24</v>
       </c>
+      <c r="Q9">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -911,6 +934,9 @@
       <c r="L11">
         <v>1</v>
       </c>
+      <c r="Q11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -949,6 +975,9 @@
       <c r="P12">
         <v>1</v>
       </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1028,6 +1057,9 @@
       <c r="P14">
         <v>1</v>
       </c>
+      <c r="Q14">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1078,6 +1110,9 @@
       <c r="O15">
         <v>4</v>
       </c>
+      <c r="Q15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1122,6 +1157,9 @@
       <c r="O16">
         <v>2</v>
       </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1145,6 +1183,9 @@
       <c r="N17">
         <v>1</v>
       </c>
+      <c r="Q17">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1232,6 +1273,9 @@
       <c r="P20">
         <v>1</v>
       </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1317,6 +1361,9 @@
       <c r="O22">
         <v>2</v>
       </c>
+      <c r="Q22">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1393,6 +1440,9 @@
       <c r="P24">
         <v>36</v>
       </c>
+      <c r="Q24">
+        <v>35</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1457,6 +1507,9 @@
       <c r="O26">
         <v>1</v>
       </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1495,6 +1548,9 @@
       <c r="J27">
         <v>174</v>
       </c>
+      <c r="K27">
+        <v>193</v>
+      </c>
       <c r="L27">
         <v>214</v>
       </c>
@@ -1510,6 +1566,9 @@
       <c r="P27">
         <v>173</v>
       </c>
+      <c r="Q27">
+        <v>123</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1545,6 +1604,9 @@
       <c r="P28">
         <v>19</v>
       </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1601,6 +1663,9 @@
       <c r="P29">
         <v>0</v>
       </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1618,6 +1683,9 @@
           <t>ESE HOSPITAL UNIVERSITARIO SAN JORGE DE PEREIRA</t>
         </is>
       </c>
+      <c r="D30">
+        <v>34</v>
+      </c>
       <c r="E30">
         <v>29</v>
       </c>
@@ -1710,6 +1778,9 @@
       <c r="P31">
         <v>0</v>
       </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1766,6 +1837,9 @@
       <c r="P32">
         <v>54</v>
       </c>
+      <c r="Q32">
+        <v>56</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1819,6 +1893,9 @@
       <c r="P33">
         <v>18</v>
       </c>
+      <c r="Q33">
+        <v>11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1872,6 +1949,9 @@
       <c r="P34">
         <v>9</v>
       </c>
+      <c r="Q34">
+        <v>6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1890,7 +1970,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E35">
         <v>78</v>
@@ -1919,11 +1999,17 @@
       <c r="M35">
         <v>51</v>
       </c>
+      <c r="N35">
+        <v>55</v>
+      </c>
       <c r="O35">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="P35">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="Q35">
+        <v>38</v>
       </c>
     </row>
     <row r="36">
@@ -1980,6 +2066,9 @@
       <c r="P37">
         <v>2</v>
       </c>
+      <c r="Q37">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2068,6 +2157,9 @@
       <c r="P39">
         <v>48</v>
       </c>
+      <c r="Q39">
+        <v>68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2124,6 +2216,9 @@
       <c r="P40">
         <v>44</v>
       </c>
+      <c r="Q40">
+        <v>54</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2180,6 +2275,9 @@
       <c r="P41">
         <v>18</v>
       </c>
+      <c r="Q41">
+        <v>17</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2292,6 +2390,9 @@
       <c r="P43">
         <v>30</v>
       </c>
+      <c r="Q43">
+        <v>39</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2348,6 +2449,9 @@
       <c r="P44">
         <v>115</v>
       </c>
+      <c r="Q44">
+        <v>124</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2404,6 +2508,9 @@
       <c r="P45">
         <v>5</v>
       </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2460,6 +2567,9 @@
       <c r="P46">
         <v>95</v>
       </c>
+      <c r="Q46">
+        <v>69</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2478,7 +2588,7 @@
         </is>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J47">
         <v>15</v>
@@ -2501,6 +2611,9 @@
       <c r="P47">
         <v>39</v>
       </c>
+      <c r="Q47">
+        <v>58</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2557,6 +2670,9 @@
       <c r="P48">
         <v>1</v>
       </c>
+      <c r="Q48">
+        <v>4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2613,6 +2729,9 @@
       <c r="P49">
         <v>0</v>
       </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2666,6 +2785,9 @@
       <c r="P50">
         <v>2</v>
       </c>
+      <c r="Q50">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2775,6 +2897,9 @@
       <c r="P52">
         <v>1</v>
       </c>
+      <c r="Q52">
+        <v>5</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2831,6 +2956,9 @@
       <c r="P53">
         <v>0</v>
       </c>
+      <c r="Q53">
+        <v>4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2887,6 +3015,9 @@
       <c r="P54">
         <v>0</v>
       </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2943,6 +3074,9 @@
       <c r="P55">
         <v>10</v>
       </c>
+      <c r="Q55">
+        <v>18</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2960,6 +3094,9 @@
           <t>SANIDAD POLICIA NACIONAL RISARALDA</t>
         </is>
       </c>
+      <c r="D56">
+        <v>31</v>
+      </c>
       <c r="E56">
         <v>10</v>
       </c>
@@ -2996,6 +3133,9 @@
       <c r="P56">
         <v>40</v>
       </c>
+      <c r="Q56">
+        <v>18</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3048,6 +3188,9 @@
       </c>
       <c r="P57">
         <v>26</v>
+      </c>
+      <c r="Q57">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
+++ b/Boletin_ Epi_Pereira/Datos/revision_IRAExt_semanal.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -440,6 +440,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -572,6 +577,9 @@
       <c r="Q4">
         <v>46</v>
       </c>
+      <c r="R4">
+        <v>41</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -607,6 +615,9 @@
       <c r="P5">
         <v>0</v>
       </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,6 +674,9 @@
       <c r="Q6">
         <v>2</v>
       </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -722,6 +736,9 @@
       <c r="Q7">
         <v>34</v>
       </c>
+      <c r="R7">
+        <v>45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -781,6 +798,9 @@
       <c r="Q8">
         <v>26</v>
       </c>
+      <c r="R8">
+        <v>35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -840,6 +860,9 @@
       <c r="Q9">
         <v>13</v>
       </c>
+      <c r="R9">
+        <v>16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -890,6 +913,9 @@
       <c r="N10">
         <v>1</v>
       </c>
+      <c r="R10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -937,6 +963,9 @@
       <c r="Q11">
         <v>2</v>
       </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -978,6 +1007,9 @@
       <c r="Q12">
         <v>1</v>
       </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1113,6 +1145,9 @@
       <c r="Q15">
         <v>2</v>
       </c>
+      <c r="R15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1186,6 +1221,9 @@
       <c r="Q17">
         <v>2</v>
       </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1224,6 +1262,9 @@
       <c r="O18">
         <v>4</v>
       </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1364,6 +1405,9 @@
       <c r="Q22">
         <v>4</v>
       </c>
+      <c r="R22">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1443,6 +1487,9 @@
       <c r="Q24">
         <v>35</v>
       </c>
+      <c r="R24">
+        <v>39</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1569,6 +1616,9 @@
       <c r="Q27">
         <v>123</v>
       </c>
+      <c r="R27">
+        <v>256</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1607,6 +1657,9 @@
       <c r="Q28">
         <v>3</v>
       </c>
+      <c r="R28">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1666,6 +1719,9 @@
       <c r="Q29">
         <v>0</v>
       </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1722,6 +1778,9 @@
       <c r="P30">
         <v>36</v>
       </c>
+      <c r="Q30">
+        <v>32</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1840,6 +1899,9 @@
       <c r="Q32">
         <v>56</v>
       </c>
+      <c r="R32">
+        <v>47</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1896,6 +1958,9 @@
       <c r="Q33">
         <v>11</v>
       </c>
+      <c r="R33">
+        <v>10</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1952,6 +2017,9 @@
       <c r="Q34">
         <v>6</v>
       </c>
+      <c r="R34">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2011,6 +2079,9 @@
       <c r="Q35">
         <v>38</v>
       </c>
+      <c r="R35">
+        <v>40</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2069,6 +2140,9 @@
       <c r="Q37">
         <v>3</v>
       </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2160,6 +2234,9 @@
       <c r="Q39">
         <v>68</v>
       </c>
+      <c r="R39">
+        <v>60</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2219,6 +2296,9 @@
       <c r="Q40">
         <v>54</v>
       </c>
+      <c r="R40">
+        <v>41</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2278,6 +2358,9 @@
       <c r="Q41">
         <v>17</v>
       </c>
+      <c r="R41">
+        <v>23</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2334,6 +2417,12 @@
       <c r="P42">
         <v>167</v>
       </c>
+      <c r="Q42">
+        <v>135</v>
+      </c>
+      <c r="R42">
+        <v>121</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2393,6 +2482,9 @@
       <c r="Q43">
         <v>39</v>
       </c>
+      <c r="R43">
+        <v>29</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2452,6 +2544,9 @@
       <c r="Q44">
         <v>124</v>
       </c>
+      <c r="R44">
+        <v>102</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2511,6 +2606,9 @@
       <c r="Q45">
         <v>1</v>
       </c>
+      <c r="R45">
+        <v>2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2570,6 +2668,9 @@
       <c r="Q46">
         <v>69</v>
       </c>
+      <c r="R46">
+        <v>61</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2614,6 +2715,9 @@
       <c r="Q47">
         <v>58</v>
       </c>
+      <c r="R47">
+        <v>33</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2673,6 +2777,9 @@
       <c r="Q48">
         <v>4</v>
       </c>
+      <c r="R48">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2732,6 +2839,9 @@
       <c r="Q49">
         <v>0</v>
       </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2788,6 +2898,9 @@
       <c r="Q50">
         <v>3</v>
       </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2900,6 +3013,9 @@
       <c r="Q52">
         <v>5</v>
       </c>
+      <c r="R52">
+        <v>4</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2959,6 +3075,9 @@
       <c r="Q53">
         <v>4</v>
       </c>
+      <c r="R53">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3018,6 +3137,9 @@
       <c r="Q54">
         <v>0</v>
       </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3077,6 +3199,9 @@
       <c r="Q55">
         <v>18</v>
       </c>
+      <c r="R55">
+        <v>16</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3136,6 +3261,9 @@
       <c r="Q56">
         <v>18</v>
       </c>
+      <c r="R56">
+        <v>18</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3191,6 +3319,9 @@
       </c>
       <c r="Q57">
         <v>16</v>
+      </c>
+      <c r="R57">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
